--- a/artfynd/A 59489-2025 artfynd.xlsx
+++ b/artfynd/A 59489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115891568</v>
+        <v>115891571</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531935</v>
+        <v>532110</v>
       </c>
       <c r="R2" t="n">
-        <v>7235025</v>
+        <v>7235023</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115891604</v>
+        <v>115891562</v>
       </c>
       <c r="B3" t="n">
-        <v>77852</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>498</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532035</v>
+        <v>531790</v>
       </c>
       <c r="R3" t="n">
-        <v>7234993</v>
+        <v>7235030</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115891601</v>
+        <v>115891604</v>
       </c>
       <c r="B4" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531996</v>
+        <v>532035</v>
       </c>
       <c r="R4" t="n">
-        <v>7234995</v>
+        <v>7234993</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115891583</v>
+        <v>115891597</v>
       </c>
       <c r="B5" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532036</v>
+        <v>531913</v>
       </c>
       <c r="R5" t="n">
-        <v>7235009</v>
+        <v>7234999</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115891602</v>
+        <v>115891576</v>
       </c>
       <c r="B6" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531915</v>
+        <v>532161</v>
       </c>
       <c r="R6" t="n">
-        <v>7234995</v>
+        <v>7235013</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115891571</v>
+        <v>115891608</v>
       </c>
       <c r="B7" t="n">
-        <v>74634</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>306</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532110</v>
+        <v>531878</v>
       </c>
       <c r="R7" t="n">
-        <v>7235023</v>
+        <v>7234984</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1341,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115891607</v>
+        <v>115891584</v>
       </c>
       <c r="B8" t="n">
-        <v>74459</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>531996</v>
+        <v>532153</v>
       </c>
       <c r="R8" t="n">
-        <v>7234986</v>
+        <v>7235008</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115891574</v>
+        <v>115891601</v>
       </c>
       <c r="B9" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>531803</v>
+        <v>531996</v>
       </c>
       <c r="R9" t="n">
-        <v>7235020</v>
+        <v>7234995</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1541,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115891599</v>
+        <v>115891602</v>
       </c>
       <c r="B10" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532114</v>
+        <v>531915</v>
       </c>
       <c r="R10" t="n">
-        <v>7234996</v>
+        <v>7234995</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1674,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115891562</v>
+        <v>115891609</v>
       </c>
       <c r="B11" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>531790</v>
+        <v>532132</v>
       </c>
       <c r="R11" t="n">
-        <v>7235030</v>
+        <v>7234983</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1763,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115891596</v>
+        <v>115891570</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,39 +1746,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532131</v>
+        <v>532110</v>
       </c>
       <c r="R12" t="n">
-        <v>7235000</v>
+        <v>7235023</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1868,11 +1808,6 @@
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1884,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1906,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115891570</v>
+        <v>115891574</v>
       </c>
       <c r="B13" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532110</v>
+        <v>531803</v>
       </c>
       <c r="R13" t="n">
-        <v>7235023</v>
+        <v>7235020</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1995,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2017,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115891598</v>
+        <v>115891599</v>
       </c>
       <c r="B14" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2166</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532112</v>
+        <v>532114</v>
       </c>
       <c r="R14" t="n">
-        <v>7234997</v>
+        <v>7234996</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2128,37 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115891559</v>
+        <v>115891587</v>
       </c>
       <c r="B15" t="n">
-        <v>104722</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2168,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>531794</v>
+        <v>531911</v>
       </c>
       <c r="R15" t="n">
-        <v>7235033</v>
+        <v>7235007</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,7 +2137,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2239,37 +2159,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115891587</v>
+        <v>115891598</v>
       </c>
       <c r="B16" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>2166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2279,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>531911</v>
+        <v>532112</v>
       </c>
       <c r="R16" t="n">
-        <v>7235007</v>
+        <v>7234997</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2328,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,15 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891606</v>
+        <v>115891583</v>
       </c>
       <c r="B17" t="n">
-        <v>94071</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>531909</v>
+        <v>532036</v>
       </c>
       <c r="R17" t="n">
-        <v>7234989</v>
+        <v>7235009</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2439,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2461,37 +2371,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891597</v>
+        <v>115891606</v>
       </c>
       <c r="B18" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>2813</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>531913</v>
+        <v>531909</v>
       </c>
       <c r="R18" t="n">
-        <v>7234999</v>
+        <v>7234989</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2550,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2572,37 +2477,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891608</v>
+        <v>115891568</v>
       </c>
       <c r="B19" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2612,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>531878</v>
+        <v>531935</v>
       </c>
       <c r="R19" t="n">
-        <v>7234984</v>
+        <v>7235025</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2661,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2676,6 +2576,776 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115891582</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>532147</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7235009</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>7261</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115891607</v>
+      </c>
+      <c r="B21" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>531996</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7234986</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>7325</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115891596</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>532131</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7235000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>7283</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127682185</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergsjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>532011</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7234912</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127682186</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergsjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>532000</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7234918</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127682187</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergsjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>531968</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7234929</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115891559</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>531794</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7235033</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
